--- a/Отчёты/097_Отчёт.xlsx
+++ b/Отчёты/097_Отчёт.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -564,12 +564,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>НУД ROI 5, № канала (8044.6)</t>
+          <t>НУД ROI 5, № канала (7936.8)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>759</t>
         </is>
       </c>
     </row>
@@ -738,6 +738,18 @@
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Отсутствует</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Fon</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>0.038</t>
         </is>
       </c>
     </row>
